--- a/output/classification/temporal=false-retriever=false-summarizer=false/results.xlsx
+++ b/output/classification/temporal=false-retriever=false-summarizer=false/results.xlsx
@@ -413,69 +413,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>temporal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>retriever</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>search</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>rerank</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>query</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>summarizer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>configuration</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>predict_f1_macro</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>predict_accuracy</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="b">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B2" t="b">
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -499,432 +504,678 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Llama-3.1-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>mode-fine_tune_bs8_lr3e-4_ep3</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5909315096507214</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Mistral-7B-Instruct-v0.3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>mode-fine_tune_bs8_lr3e-4_ep2</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5049291566532946</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>ModernBERT-base</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>bs8_lr3e-5_ep5</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J4" t="n">
         <v>0.5858977587181075</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K4" t="n">
         <v>0.7055214723926381</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="b">
-        <v>0</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Qwen3.5-9B-Base</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>mode-fine_tune_bs8_lr1e-4_ep3</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>RooseBERT-cont-cased</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>bs16_lr2e-5_ep3</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J6" t="n">
         <v>0.03642987249544626</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K6" t="n">
         <v>0.1226993865030675</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="b">
-        <v>0</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>RooseBERT-cont-uncased</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>bs16_lr2e-5_ep3</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J7" t="n">
         <v>0.03642987249544626</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K7" t="n">
         <v>0.1226993865030675</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="b">
-        <v>0</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B8" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>RooseBERT-scr-cased</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>bs16_lr2e-5_ep3</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J8" t="n">
         <v>0.03642987249544626</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K8" t="n">
         <v>0.1226993865030675</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="b">
-        <v>0</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B9" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>RooseBERT-scr-uncased</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>bs16_lr2e-5_ep3</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J9" t="n">
         <v>0.03642987249544626</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K9" t="n">
         <v>0.1226993865030675</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="b">
-        <v>0</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B10" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>deberta-v3-base</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>bs16_lr2e-5_ep5</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J10" t="n">
         <v>0.1202614379084967</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K10" t="n">
         <v>0.5644171779141104</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="b">
-        <v>0</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>mode-fine_tune_bs8_lr5e-4_ep1</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4642182799045544</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B12" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>legalbert</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>bs8_lr5e-5_ep5</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="J12" t="n">
         <v>0.698635008996851</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K12" t="n">
         <v>0.7791411042944786</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="b">
-        <v>0</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>longformer-base-4096</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>bs8_lr5e-5_ep5</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="J13" t="n">
         <v>0.6758715268089439</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K13" t="n">
         <v>0.7730061349693251</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="b">
-        <v>0</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>roberta-base</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>bs8_lr5e-5_ep5</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="J14" t="n">
         <v>0.649756830779871</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K14" t="n">
         <v>0.7668711656441718</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="b">
-        <v>0</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>output/classification/temporal=false-retriever=false-summarizer=false</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>xlm-roberta-base</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>bs8_lr3e-5_ep5</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="J15" t="n">
         <v>0.4301195988797067</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K15" t="n">
         <v>0.50920245398773</v>
       </c>
     </row>
